--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5EC142-D002-294E-BEA1-41D20F08F58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039B5246-1E1D-EF44-A08E-3740814CD74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="32860" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
@@ -335,9 +335,6 @@
     <t>RKRB-44</t>
   </si>
   <si>
-    <t>SupervisorDespacho</t>
-  </si>
-  <si>
     <t>KCFD-62</t>
   </si>
   <si>
@@ -825,6 +822,9 @@
   </si>
   <si>
     <t>JMEDINA</t>
+  </si>
+  <si>
+    <t>Supervisor Despacho</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1112,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4EB4D5A9-85E8-224A-ABD7-ADB55BC98781}" name="Tabla3" displayName="Tabla3" ref="A1:T231" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5">
-  <autoFilter ref="A1:T231" xr:uid="{4EB4D5A9-85E8-224A-ABD7-ADB55BC98781}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{1F0B7E48-3D94-9E48-8ACE-382CC0D1BB68}" name="Nº Operación"/>
     <tableColumn id="2" xr3:uid="{598C855D-7599-3841-B923-15A0B483C8B3}" name="Fecha"/>
@@ -1129,7 +1128,7 @@
     <tableColumn id="12" xr3:uid="{F7DD7FC6-533C-6446-82BA-1BD09906476C}" name="DTE"/>
     <tableColumn id="10" xr3:uid="{A16972AF-AEE9-BF46-8A14-3D047B9F1F18}" name="Entrega"/>
     <tableColumn id="13" xr3:uid="{0A210B13-6D66-F141-BB08-D066EA1ACEF8}" name="Qty Entrega"/>
-    <tableColumn id="11" xr3:uid="{B059AADE-B32A-3643-B307-32F73D312A41}" name="SupervisorDespacho" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{B059AADE-B32A-3643-B307-32F73D312A41}" name="Supervisor Despacho" dataDxfId="4"/>
     <tableColumn id="19" xr3:uid="{520C7406-2FBF-344D-B6E8-8DED0C551A54}" name="Tiempo atención Despacho (mins)" dataDxfId="3"/>
     <tableColumn id="18" xr3:uid="{9E2FE814-36D5-DF46-A381-CBD8475D7F80}" name="Tiempo atención Expedición (mins)" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{EB971EAB-E799-2049-B0D8-067E6B35A91E}" name="Comentario Despacho" dataDxfId="1"/>
@@ -1439,26 +1438,26 @@
   <dimension ref="A1:T231"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="38" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1508,7 +1507,7 @@
         <v>12</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>100</v>
+        <v>263</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>32</v>
@@ -1546,10 +1545,10 @@
         <v>800000013</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="J2" s="5">
         <v>5.618055555555556E-2</v>
@@ -1558,7 +1557,7 @@
         <v>1.7557870370370373E-2</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M2" s="1">
         <v>123110</v>
@@ -1570,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q2" s="2">
         <v>22.1</v>
@@ -1579,10 +1578,10 @@
         <v>0.183</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
@@ -1608,10 +1607,10 @@
         <v>800000013</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J3" s="5">
         <v>3.3900462962962966E-2</v>
@@ -1620,7 +1619,7 @@
         <v>3.1122685185185187E-2</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M3" s="1">
         <v>123109</v>
@@ -1632,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q3" s="2">
         <v>41.567</v>
@@ -1641,10 +1640,10 @@
         <v>0.15</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
@@ -1673,7 +1672,7 @@
         <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J4" s="5">
         <v>5.1412037037037034E-2</v>
@@ -1682,7 +1681,7 @@
         <v>4.7511574074074074E-2</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M4" s="1">
         <v>123108</v>
@@ -1694,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q4" s="2">
         <v>65.316999999999993</v>
@@ -1703,10 +1702,10 @@
         <v>0.15</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
@@ -1735,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J5" s="5">
         <v>6.5439814814814812E-2</v>
@@ -1744,7 +1743,7 @@
         <v>2.164351851851852E-2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M5" s="1">
         <v>123107</v>
@@ -1756,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q5" s="2">
         <v>26</v>
@@ -1765,10 +1764,10 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -1797,7 +1796,7 @@
         <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J6" s="5">
         <v>2.6446759259259264E-2</v>
@@ -1806,7 +1805,7 @@
         <v>2.8506944444444442E-2</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M6" s="1">
         <v>123106</v>
@@ -1818,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q6" s="2">
         <v>32.567</v>
@@ -1827,10 +1826,10 @@
         <v>0.217</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
@@ -1859,7 +1858,7 @@
         <v>44</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J7" s="5">
         <v>7.7812499999999993E-2</v>
@@ -1868,7 +1867,7 @@
         <v>1.1423611111111112E-2</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M7" s="1">
         <v>123105</v>
@@ -1880,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q7" s="2">
         <v>9.3170000000000002</v>
@@ -1889,10 +1888,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
@@ -1921,7 +1920,7 @@
         <v>24</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J8" s="5">
         <v>3.8715277777777779E-2</v>
@@ -1930,7 +1929,7 @@
         <v>2.8483796296296295E-2</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M8" s="1">
         <v>123104</v>
@@ -1942,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q8" s="2">
         <v>32.183</v>
@@ -1951,10 +1950,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
@@ -1983,7 +1982,7 @@
         <v>31</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J9" s="5">
         <v>2.9687500000000002E-2</v>
@@ -1992,7 +1991,7 @@
         <v>2.4884259259259259E-2</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M9" s="1">
         <v>123103</v>
@@ -2004,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q9" s="2">
         <v>27.483000000000001</v>
@@ -2013,10 +2012,10 @@
         <v>0.2</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
@@ -2066,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q10" s="2">
         <v>29.882999999999999</v>
@@ -2075,10 +2074,10 @@
         <v>20.100000000000001</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
@@ -2128,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q11" s="2">
         <v>29.65</v>
@@ -2137,10 +2136,10 @@
         <v>1.133</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -2169,7 +2168,7 @@
         <v>43</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J12" s="5">
         <v>0.26923611111111112</v>
@@ -2178,7 +2177,7 @@
         <v>3.2476851851851847E-2</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M12" s="1">
         <v>123099</v>
@@ -2190,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q12" s="2">
         <v>1.1000000000000001</v>
@@ -2199,10 +2198,10 @@
         <v>39.5</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
@@ -2252,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q13" s="2">
         <v>45.767000000000003</v>
@@ -2261,10 +2260,10 @@
         <v>0.1</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
@@ -2293,7 +2292,7 @@
         <v>26</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J14" s="5">
         <v>0.42003472222222221</v>
@@ -2302,7 +2301,7 @@
         <v>3.8715277777777779E-2</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M14" s="1">
         <v>123098</v>
@@ -2314,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q14" s="2">
         <v>50.55</v>
@@ -2323,10 +2322,10 @@
         <v>0.2</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
@@ -2355,7 +2354,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J15" s="5">
         <v>0.43931712962962965</v>
@@ -2364,7 +2363,7 @@
         <v>7.6736111111111111E-3</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M15" s="1">
         <v>123097</v>
@@ -2376,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q15" s="2">
         <v>5.7830000000000004</v>
@@ -2385,10 +2384,10 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
@@ -2438,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q16" s="2">
         <v>51.832999999999998</v>
@@ -2447,10 +2446,10 @@
         <v>0.1</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -2500,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q17" s="2">
         <v>63.332999999999998</v>
@@ -2509,10 +2508,10 @@
         <v>0.1</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -2541,7 +2540,7 @@
         <v>22</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J18" s="5">
         <v>0.10046296296296296</v>
@@ -2550,7 +2549,7 @@
         <v>4.7407407407407405E-2</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="1">
         <v>123094</v>
@@ -2562,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q18" s="2">
         <v>66.617000000000004</v>
@@ -2571,10 +2570,10 @@
         <v>0.2</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -2603,7 +2602,7 @@
         <v>22</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" s="5">
         <v>7.0775462962962957E-2</v>
@@ -2612,7 +2611,7 @@
         <v>4.4594907407407409E-2</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M19" s="1">
         <v>123093</v>
@@ -2624,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q19" s="2">
         <v>61.616999999999997</v>
@@ -2633,10 +2632,10 @@
         <v>0.1</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
@@ -2686,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q20" s="2">
         <v>38.549999999999997</v>
@@ -2695,10 +2694,10 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
@@ -2748,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q21" s="2">
         <v>65.45</v>
@@ -2757,10 +2756,10 @@
         <v>16.117000000000001</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -2789,7 +2788,7 @@
         <v>22</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J22" s="5">
         <v>2.2499999999999996E-2</v>
@@ -2798,7 +2797,7 @@
         <v>4.7037037037037037E-2</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M22" s="1">
         <v>123090</v>
@@ -2810,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q22" s="2">
         <v>53.783000000000001</v>
@@ -2819,10 +2818,10 @@
         <v>12.467000000000001</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
@@ -2872,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q23" s="2">
         <v>23.4</v>
@@ -2881,10 +2880,10 @@
         <v>24.417000000000002</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -2913,7 +2912,7 @@
         <v>39</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J24" s="5">
         <v>0.24800925925925923</v>
@@ -2922,7 +2921,7 @@
         <v>3.1909722222222221E-2</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M24" s="1">
         <v>123088</v>
@@ -2934,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q24" s="2">
         <v>31.667000000000002</v>
@@ -2943,10 +2942,10 @@
         <v>5.7670000000000003</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -2996,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q25" s="2">
         <v>34.067</v>
@@ -3005,10 +3004,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
@@ -3058,7 +3057,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q26" s="2">
         <v>33.133000000000003</v>
@@ -3067,10 +3066,10 @@
         <v>5.2670000000000003</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
@@ -3129,10 +3128,10 @@
         <v>26.683</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
@@ -3191,10 +3190,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
@@ -3223,7 +3222,7 @@
         <v>43</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J29" s="5">
         <v>0.2210648148148148</v>
@@ -3232,7 +3231,7 @@
         <v>5.094907407407407E-2</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M29" s="1">
         <v>123083</v>
@@ -3253,10 +3252,10 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
@@ -3315,10 +3314,10 @@
         <v>17.7</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
@@ -3347,7 +3346,7 @@
         <v>29</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J31" s="5">
         <v>0.20024305555555555</v>
@@ -3356,7 +3355,7 @@
         <v>4.8645833333333333E-2</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M31" s="1">
         <v>123081</v>
@@ -3377,10 +3376,10 @@
         <v>11.217000000000001</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
@@ -3409,7 +3408,7 @@
         <v>29</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J32" s="5">
         <v>0.20045138888888889</v>
@@ -3418,7 +3417,7 @@
         <v>4.0740740740740737E-2</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M32" s="1">
         <v>123080</v>
@@ -3439,10 +3438,10 @@
         <v>2.7</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
@@ -3471,7 +3470,7 @@
         <v>26</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J33" s="5">
         <v>0.16836805555555556</v>
@@ -3480,7 +3479,7 @@
         <v>5.3263888888888888E-2</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M33" s="1">
         <v>123078</v>
@@ -3501,10 +3500,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
@@ -3533,7 +3532,7 @@
         <v>43</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J34" s="5">
         <v>0.10103009259259259</v>
@@ -3542,7 +3541,7 @@
         <v>3.802083333333333E-2</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M34" s="1">
         <v>123077</v>
@@ -3563,10 +3562,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
@@ -3595,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J35" s="5">
         <v>0.15055555555555555</v>
@@ -3604,7 +3603,7 @@
         <v>6.1354166666666675E-2</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M35" s="1">
         <v>123076</v>
@@ -3625,10 +3624,10 @@
         <v>19.283000000000001</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
@@ -3657,7 +3656,7 @@
         <v>26</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J36" s="5">
         <v>0.18789351851851852</v>
@@ -3666,7 +3665,7 @@
         <v>2.162037037037037E-2</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M36" s="1">
         <v>123075</v>
@@ -3687,10 +3686,10 @@
         <v>0.217</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
@@ -3719,7 +3718,7 @@
         <v>29</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J37" s="5">
         <v>0.14186342592592593</v>
@@ -3728,7 +3727,7 @@
         <v>3.0520833333333334E-2</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M37" s="1">
         <v>123074</v>
@@ -3749,10 +3748,10 @@
         <v>0.15</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
@@ -3811,10 +3810,10 @@
         <v>0.317</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3873,10 +3872,10 @@
         <v>2.0670000000000002</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
@@ -3935,10 +3934,10 @@
         <v>8.0169999999999995</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
@@ -3976,7 +3975,7 @@
         <v>3.4097222222222223E-2</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M41" s="1">
         <v>123071</v>
@@ -3997,10 +3996,10 @@
         <v>11.167</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
@@ -4059,10 +4058,10 @@
         <v>24.766999999999999</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
@@ -4091,7 +4090,7 @@
         <v>26</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J43" s="5">
         <v>5.0254629629629628E-2</v>
@@ -4100,7 +4099,7 @@
         <v>5.9166666666666666E-2</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M43" s="1">
         <v>123070</v>
@@ -4121,10 +4120,10 @@
         <v>0.2</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
@@ -4153,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J44" s="5">
         <v>5.67824074074074E-2</v>
@@ -4162,7 +4161,7 @@
         <v>7.1180555555555566E-2</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M44" s="1">
         <v>123069</v>
@@ -4183,10 +4182,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
@@ -4224,7 +4223,7 @@
         <v>1.1562499999999998E-2</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M45" s="1">
         <v>53094</v>
@@ -4245,10 +4244,10 @@
         <v>0.25</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
@@ -4307,10 +4306,10 @@
         <v>22.516999999999999</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
@@ -4339,7 +4338,7 @@
         <v>21</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J47" s="5">
         <v>3.6527777777777777E-2</v>
@@ -4348,7 +4347,7 @@
         <v>3.7303240740740741E-2</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M47" s="1">
         <v>123068</v>
@@ -4369,10 +4368,10 @@
         <v>22.082999999999998</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
@@ -4431,10 +4430,10 @@
         <v>22.45</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
@@ -4493,10 +4492,10 @@
         <v>0.2</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
@@ -4534,7 +4533,7 @@
         <v>2.148148148148148E-2</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M50" s="1">
         <v>53089</v>
@@ -4555,10 +4554,10 @@
         <v>10.5</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
@@ -4587,7 +4586,7 @@
         <v>41</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J51" s="5">
         <v>4.1284722222222223E-2</v>
@@ -4596,7 +4595,7 @@
         <v>0.11721064814814815</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M51" s="1">
         <v>123066</v>
@@ -4608,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q51" s="2">
         <v>157.55000000000001</v>
@@ -4617,10 +4616,10 @@
         <v>0.2</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
@@ -4649,7 +4648,7 @@
         <v>23</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J52" s="5">
         <v>2.449074074074074E-2</v>
@@ -4679,10 +4678,10 @@
         <v>0.15</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
@@ -4732,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q53" s="2">
         <v>4.1829999999999998</v>
@@ -4741,10 +4740,10 @@
         <v>24.9</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
@@ -4794,7 +4793,7 @@
         <v>1</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q54" s="2">
         <v>18.183</v>
@@ -4803,10 +4802,10 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
@@ -4844,7 +4843,7 @@
         <v>1.300925925925926E-2</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M55" s="1">
         <v>53086</v>
@@ -4856,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q55" s="2">
         <v>11.95</v>
@@ -4865,10 +4864,10 @@
         <v>0.183</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
@@ -4918,7 +4917,7 @@
         <v>1</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q56" s="2">
         <v>33.517000000000003</v>
@@ -4927,10 +4926,10 @@
         <v>0.217</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
@@ -4959,7 +4958,7 @@
         <v>23</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J57" s="5">
         <v>3.4918981481481481E-2</v>
@@ -4980,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q57" s="2">
         <v>8.9499999999999993</v>
@@ -4989,10 +4988,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
@@ -5042,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q58" s="2">
         <v>21.132999999999999</v>
@@ -5051,10 +5050,10 @@
         <v>0.217</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
@@ -5092,7 +5091,7 @@
         <v>1.6122685185185184E-2</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M59" s="1">
         <v>53083</v>
@@ -5104,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q59" s="2">
         <v>16.683</v>
@@ -5113,10 +5112,10 @@
         <v>0.183</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
@@ -5166,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q60" s="2">
         <v>26.466999999999999</v>
@@ -5175,10 +5174,10 @@
         <v>6.1</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
@@ -5207,7 +5206,7 @@
         <v>27</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J61" s="5">
         <v>1.1990740740740739E-2</v>
@@ -5216,7 +5215,7 @@
         <v>3.1261574074074074E-2</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M61" s="1">
         <v>123062</v>
@@ -5228,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q61" s="2">
         <v>33.917000000000002</v>
@@ -5237,10 +5236,10 @@
         <v>2.8</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
@@ -5290,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q62" s="2">
         <v>30.216999999999999</v>
@@ -5299,10 +5298,10 @@
         <v>0.1</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
@@ -5352,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q63" s="2">
         <v>16.266999999999999</v>
@@ -5361,10 +5360,10 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
@@ -5414,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q64" s="2">
         <v>45.167000000000002</v>
@@ -5423,10 +5422,10 @@
         <v>8.2170000000000005</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
@@ -5455,7 +5454,7 @@
         <v>24</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J65" s="5">
         <v>5.4513888888888884E-3</v>
@@ -5476,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q65" s="2">
         <v>50.75</v>
@@ -5485,10 +5484,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
@@ -5538,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q66" s="2">
         <v>20.45</v>
@@ -5547,10 +5546,10 @@
         <v>6.7329999999999997</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
@@ -5600,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q67" s="2">
         <v>77.766999999999996</v>
@@ -5609,10 +5608,10 @@
         <v>6.4169999999999998</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
@@ -5641,7 +5640,7 @@
         <v>29</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J68" s="5">
         <v>3.650462962962963E-2</v>
@@ -5650,7 +5649,7 @@
         <v>2.2094907407407407E-2</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M68" s="1">
         <v>123055</v>
@@ -5662,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q68" s="2">
         <v>23.3</v>
@@ -5671,10 +5670,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
@@ -5724,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q69" s="2">
         <v>31.266999999999999</v>
@@ -5733,10 +5732,10 @@
         <v>0.1</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
@@ -5765,7 +5764,7 @@
         <v>22</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J70" s="5">
         <v>1.6620370370370372E-2</v>
@@ -5774,7 +5773,7 @@
         <v>1.4513888888888889E-2</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M70" s="1">
         <v>123053</v>
@@ -5786,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q70" s="2">
         <v>11.433</v>
@@ -5795,10 +5794,10 @@
         <v>4.383</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
@@ -5848,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q71" s="2">
         <v>32.582999999999998</v>
@@ -5857,10 +5856,10 @@
         <v>12.3</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
@@ -5919,10 +5918,10 @@
         <v>0.68300000000000005</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T72" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
@@ -5981,10 +5980,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T73" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
@@ -6013,7 +6012,7 @@
         <v>26</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J74" s="5">
         <v>0.20055555555555557</v>
@@ -6022,7 +6021,7 @@
         <v>2.326388888888889E-2</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M74" s="1">
         <v>123049</v>
@@ -6043,10 +6042,10 @@
         <v>5.0670000000000002</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T74" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
@@ -6105,10 +6104,10 @@
         <v>2.95</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T75" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
@@ -6137,7 +6136,7 @@
         <v>29</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J76" s="5">
         <v>0.25160879629629629</v>
@@ -6146,7 +6145,7 @@
         <v>4.1782407407407407E-2</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M76" s="1">
         <v>123047</v>
@@ -6167,10 +6166,10 @@
         <v>1.0669999999999999</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
@@ -6196,10 +6195,10 @@
         <v>800000013</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J77" s="5">
         <v>0.1386226851851852</v>
@@ -6208,7 +6207,7 @@
         <v>4.7685185185185185E-2</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M77" s="1">
         <v>123046</v>
@@ -6229,10 +6228,10 @@
         <v>3.6</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
@@ -6261,7 +6260,7 @@
         <v>28</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J78" s="5">
         <v>0.24381944444444445</v>
@@ -6270,7 +6269,7 @@
         <v>4.0092592592592589E-2</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M78" s="1">
         <v>123045</v>
@@ -6291,10 +6290,10 @@
         <v>12.817</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.2">
@@ -6323,7 +6322,7 @@
         <v>26</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J79" s="5">
         <v>0.21516203703703704</v>
@@ -6332,7 +6331,7 @@
         <v>5.1828703703703703E-2</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M79" s="1">
         <v>123044</v>
@@ -6353,10 +6352,10 @@
         <v>10.5</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T79" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
@@ -6415,10 +6414,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T80" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
@@ -6447,7 +6446,7 @@
         <v>26</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J81" s="5">
         <v>6.8692129629629631E-2</v>
@@ -6456,7 +6455,7 @@
         <v>2.7546296296296294E-2</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M81" s="1">
         <v>123042</v>
@@ -6477,10 +6476,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T81" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
@@ -6509,7 +6508,7 @@
         <v>26</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J82" s="5">
         <v>0.1816550925925926</v>
@@ -6518,7 +6517,7 @@
         <v>4.8854166666666664E-2</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M82" s="1">
         <v>123041</v>
@@ -6539,10 +6538,10 @@
         <v>20.216999999999999</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T82" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
@@ -6571,7 +6570,7 @@
         <v>75</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J83" s="5">
         <v>0.18346064814814814</v>
@@ -6580,7 +6579,7 @@
         <v>6.7777777777777784E-2</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M83" s="1">
         <v>123040</v>
@@ -6601,10 +6600,10 @@
         <v>6.15</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T83" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
@@ -6633,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J84" s="5">
         <v>0.16876157407407408</v>
@@ -6642,7 +6641,7 @@
         <v>3.1666666666666669E-2</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M84" s="1">
         <v>123039</v>
@@ -6663,10 +6662,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T84" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.2">
@@ -6704,7 +6703,7 @@
         <v>1.3969907407407408E-2</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M85" s="1">
         <v>53081</v>
@@ -6725,10 +6724,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T85" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
@@ -6787,10 +6786,10 @@
         <v>8.2330000000000005</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T86" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
@@ -6849,10 +6848,10 @@
         <v>6.4669999999999996</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T87" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
@@ -6911,10 +6910,10 @@
         <v>28.483000000000001</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T88" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.2">
@@ -6943,7 +6942,7 @@
         <v>81</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J89" s="5">
         <v>0.13621527777777778</v>
@@ -6952,7 +6951,7 @@
         <v>7.9861111111111122E-3</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M89" s="1">
         <v>123037</v>
@@ -6964,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q89" s="2">
         <v>0.1</v>
@@ -6973,10 +6972,10 @@
         <v>3.7330000000000001</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T89" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.2">
@@ -7014,7 +7013,7 @@
         <v>2.2534722222222223E-2</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M90" s="1">
         <v>53078</v>
@@ -7035,10 +7034,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T90" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.2">
@@ -7088,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q91" s="2">
         <v>46.616999999999997</v>
@@ -7097,10 +7096,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T91" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.2">
@@ -7129,7 +7128,7 @@
         <v>43</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J92" s="5">
         <v>4.4525462962962968E-2</v>
@@ -7138,7 +7137,7 @@
         <v>5.5115740740740743E-2</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M92" s="1">
         <v>123034</v>
@@ -7159,10 +7158,10 @@
         <v>16.899999999999999</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T92" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.2">
@@ -7221,10 +7220,10 @@
         <v>0.183</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T93" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.2">
@@ -7283,10 +7282,10 @@
         <v>0.183</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T94" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.2">
@@ -7345,10 +7344,10 @@
         <v>0.2</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T95" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.2">
@@ -7374,10 +7373,10 @@
         <v>800000250</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J96" s="5">
         <v>3.5972222222222218E-2</v>
@@ -7386,7 +7385,7 @@
         <v>4.8865740740740737E-2</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M96" s="1">
         <v>123033</v>
@@ -7407,10 +7406,10 @@
         <v>22</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T96" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
@@ -7439,7 +7438,7 @@
         <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J97" s="5">
         <v>1.1585648148148149E-2</v>
@@ -7448,7 +7447,7 @@
         <v>5.2708333333333336E-2</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M97" s="1">
         <v>123032</v>
@@ -7469,10 +7468,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T97" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
@@ -7510,7 +7509,7 @@
         <v>1.954861111111111E-2</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M98" s="1">
         <v>53072</v>
@@ -7531,10 +7530,10 @@
         <v>20.417000000000002</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T98" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
@@ -7593,10 +7592,10 @@
         <v>13.117000000000001</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T99" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.2">
@@ -7607,7 +7606,7 @@
         <v>44624</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D100" s="5">
         <v>0.39586805555555554</v>
@@ -7625,7 +7624,7 @@
         <v>17</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J100" s="5">
         <v>8.0138888888888885E-2</v>
@@ -7634,7 +7633,7 @@
         <v>2.4652777777777776E-3</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M100" s="1">
         <v>53071</v>
@@ -7655,10 +7654,10 @@
         <v>0.5</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T100" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.2">
@@ -7717,10 +7716,10 @@
         <v>17.417000000000002</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T101" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.2">
@@ -7758,7 +7757,7 @@
         <v>1.4560185185185183E-2</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M102" s="1">
         <v>53067</v>
@@ -7770,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q102" s="2">
         <v>2.1669999999999998</v>
@@ -7779,10 +7778,10 @@
         <v>15.667</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.2">
@@ -7811,7 +7810,7 @@
         <v>24</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J103" s="5">
         <v>5.0960648148148151E-2</v>
@@ -7820,7 +7819,7 @@
         <v>3.2673611111111105E-2</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M103" s="1">
         <v>123031</v>
@@ -7832,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q103" s="2">
         <v>43.667000000000002</v>
@@ -7841,10 +7840,10 @@
         <v>0.183</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T103" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.2">
@@ -7894,7 +7893,7 @@
         <v>1</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q104" s="2">
         <v>11.4</v>
@@ -7903,10 +7902,10 @@
         <v>0.183</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T104" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.2">
@@ -7935,7 +7934,7 @@
         <v>31</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J105" s="5">
         <v>2.2037037037037036E-2</v>
@@ -7956,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q105" s="2">
         <v>52.133000000000003</v>
@@ -7965,10 +7964,10 @@
         <v>0.15</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T105" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.2">
@@ -8018,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q106" s="2">
         <v>16.433</v>
@@ -8027,10 +8026,10 @@
         <v>0.15</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T106" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.2">
@@ -8080,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q107" s="2">
         <v>26.683</v>
@@ -8089,10 +8088,10 @@
         <v>0.1</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T107" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.2">
@@ -8142,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q108" s="2">
         <v>26.466999999999999</v>
@@ -8151,10 +8150,10 @@
         <v>5.3170000000000002</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T108" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.2">
@@ -8204,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q109" s="2">
         <v>60.45</v>
@@ -8213,10 +8212,10 @@
         <v>0.1</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T109" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.2">
@@ -8266,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q110" s="2">
         <v>16.433</v>
@@ -8275,10 +8274,10 @@
         <v>16.533000000000001</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T110" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.2">
@@ -8307,7 +8306,7 @@
         <v>22</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J111" s="5">
         <v>6.5648148148148136E-2</v>
@@ -8316,7 +8315,7 @@
         <v>3.9861111111111111E-2</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M111" s="1">
         <v>123025</v>
@@ -8328,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q111" s="2">
         <v>41.683</v>
@@ -8337,10 +8336,10 @@
         <v>13.683</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T111" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.2">
@@ -8369,7 +8368,7 @@
         <v>49</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J112" s="5">
         <v>0.15327546296296296</v>
@@ -8378,7 +8377,7 @@
         <v>4.7974537037037045E-2</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M112" s="1">
         <v>123023</v>
@@ -8390,7 +8389,7 @@
         <v>1</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q112" s="2">
         <v>43.317</v>
@@ -8399,10 +8398,10 @@
         <v>20.317</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T112" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.2">
@@ -8452,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q113" s="2">
         <v>46.2</v>
@@ -8461,10 +8460,10 @@
         <v>10.766999999999999</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T113" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.2">
@@ -8514,7 +8513,7 @@
         <v>1</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q114" s="2">
         <v>52.05</v>
@@ -8523,10 +8522,10 @@
         <v>0.1</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T114" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.2">
@@ -8555,7 +8554,7 @@
         <v>21</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J115" s="5">
         <v>0.17358796296296297</v>
@@ -8564,7 +8563,7 @@
         <v>3.8807870370370375E-2</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M115" s="1">
         <v>123021</v>
@@ -8576,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q115" s="2">
         <v>51.5</v>
@@ -8585,10 +8584,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T115" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.2">
@@ -8617,7 +8616,7 @@
         <v>41</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J116" s="5">
         <v>0.13598379629629628</v>
@@ -8626,7 +8625,7 @@
         <v>3.9548611111111111E-2</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M116" s="1">
         <v>123020</v>
@@ -8638,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q116" s="2">
         <v>44.817</v>
@@ -8647,10 +8646,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T116" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.2">
@@ -8709,10 +8708,10 @@
         <v>0.1</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T117" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.2">
@@ -8741,7 +8740,7 @@
         <v>44</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J118" s="5">
         <v>5.168981481481482E-2</v>
@@ -8750,7 +8749,7 @@
         <v>9.1863425925925932E-2</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M118" s="1">
         <v>123018</v>
@@ -8771,10 +8770,10 @@
         <v>18</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T118" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.2">
@@ -8800,7 +8799,7 @@
         <v>800000250</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>93</v>
@@ -8833,10 +8832,10 @@
         <v>54.5</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T119" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.2">
@@ -8865,7 +8864,7 @@
         <v>26</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J120" s="5">
         <v>0.16979166666666667</v>
@@ -8874,7 +8873,7 @@
         <v>4.3530092592592599E-2</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M120" s="1">
         <v>123016</v>
@@ -8895,10 +8894,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T120" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.2">
@@ -8927,7 +8926,7 @@
         <v>26</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J121" s="5">
         <v>0.1469212962962963</v>
@@ -8957,10 +8956,10 @@
         <v>21.582999999999998</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T121" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.2">
@@ -8989,7 +8988,7 @@
         <v>81</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J122" s="5">
         <v>0.12314814814814816</v>
@@ -8998,7 +8997,7 @@
         <v>5.5949074074074075E-2</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M122" s="1">
         <v>123014</v>
@@ -9019,10 +9018,10 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T122" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.2">
@@ -9048,7 +9047,7 @@
         <v>800000250</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>95</v>
@@ -9081,10 +9080,10 @@
         <v>9.7829999999999995</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T123" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.2">
@@ -9110,10 +9109,10 @@
         <v>800000250</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J124" s="5">
         <v>0.11951388888888888</v>
@@ -9122,7 +9121,7 @@
         <v>4.2106481481481488E-2</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M124" s="1">
         <v>123012</v>
@@ -9143,10 +9142,10 @@
         <v>0.183</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T124" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.2">
@@ -9175,7 +9174,7 @@
         <v>43</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J125" s="5">
         <v>0.12042824074074072</v>
@@ -9184,7 +9183,7 @@
         <v>2.943287037037037E-2</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M125" s="1">
         <v>123010</v>
@@ -9205,10 +9204,10 @@
         <v>13.6</v>
       </c>
       <c r="S125" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T125" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.2">
@@ -9258,7 +9257,7 @@
         <v>1</v>
       </c>
       <c r="P126" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q126" s="2">
         <v>56.3</v>
@@ -9267,10 +9266,10 @@
         <v>19.933</v>
       </c>
       <c r="S126" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T126" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="127" spans="1:20" x14ac:dyDescent="0.2">
@@ -9308,7 +9307,7 @@
         <v>3.4421296296296297E-2</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M127" s="1">
         <v>53060</v>
@@ -9329,10 +9328,10 @@
         <v>19.516999999999999</v>
       </c>
       <c r="S127" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T127" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.2">
@@ -9382,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="P128" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q128" s="2">
         <v>24.382999999999999</v>
@@ -9391,10 +9390,10 @@
         <v>0.15</v>
       </c>
       <c r="S128" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T128" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.2">
@@ -9444,7 +9443,7 @@
         <v>1</v>
       </c>
       <c r="P129" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q129" s="2">
         <v>24.65</v>
@@ -9453,10 +9452,10 @@
         <v>0.2</v>
       </c>
       <c r="S129" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T129" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.2">
@@ -9506,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q130" s="2">
         <v>49.05</v>
@@ -9515,10 +9514,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S130" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T130" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.2">
@@ -9547,7 +9546,7 @@
         <v>22</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J131" s="5">
         <v>5.3402777777777778E-2</v>
@@ -9556,7 +9555,7 @@
         <v>5.783564814814815E-2</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M131" s="1">
         <v>123008</v>
@@ -9568,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q131" s="2">
         <v>77.582999999999998</v>
@@ -9577,10 +9576,10 @@
         <v>0.2</v>
       </c>
       <c r="S131" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T131" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.2">
@@ -9618,7 +9617,7 @@
         <v>2.1666666666666667E-2</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M132" s="1">
         <v>53054</v>
@@ -9630,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="P132" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q132" s="2">
         <v>30.317</v>
@@ -9639,10 +9638,10 @@
         <v>0.183</v>
       </c>
       <c r="S132" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T132" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.2">
@@ -9692,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q133" s="2">
         <v>12.016999999999999</v>
@@ -9701,10 +9700,10 @@
         <v>0.2</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T133" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.2">
@@ -9754,7 +9753,7 @@
         <v>1</v>
       </c>
       <c r="P134" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q134" s="2">
         <v>0.45</v>
@@ -9763,10 +9762,10 @@
         <v>0.15</v>
       </c>
       <c r="S134" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T134" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.2">
@@ -9795,7 +9794,7 @@
         <v>24</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J135" s="5">
         <v>5.0219907407407414E-2</v>
@@ -9804,7 +9803,7 @@
         <v>2.5613425925925925E-2</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M135" s="1">
         <v>123007</v>
@@ -9816,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="P135" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q135" s="2">
         <v>30.716999999999999</v>
@@ -9825,10 +9824,10 @@
         <v>0.2</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T135" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="1:20" x14ac:dyDescent="0.2">
@@ -9878,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="P136" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q136" s="2">
         <v>23.933</v>
@@ -9887,10 +9886,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T136" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.2">
@@ -9928,7 +9927,7 @@
         <v>1.638888888888889E-2</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M137" s="1">
         <v>53050</v>
@@ -9940,7 +9939,7 @@
         <v>1</v>
       </c>
       <c r="P137" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q137" s="2">
         <v>15.417</v>
@@ -9949,10 +9948,10 @@
         <v>0.15</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T137" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.2">
@@ -9981,7 +9980,7 @@
         <v>31</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J138" s="5">
         <v>8.8055555555555554E-2</v>
@@ -10002,7 +10001,7 @@
         <v>1</v>
       </c>
       <c r="P138" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q138" s="2">
         <v>0.51700000000000002</v>
@@ -10011,10 +10010,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S138" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T138" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.2">
@@ -10073,10 +10072,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S139" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T139" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.2">
@@ -10126,7 +10125,7 @@
         <v>1</v>
       </c>
       <c r="P140" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q140" s="2">
         <v>8.2330000000000005</v>
@@ -10135,10 +10134,10 @@
         <v>0.15</v>
       </c>
       <c r="S140" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T140" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.2">
@@ -10167,7 +10166,7 @@
         <v>31</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J141" s="5">
         <v>5.1064814814814813E-2</v>
@@ -10188,7 +10187,7 @@
         <v>1</v>
       </c>
       <c r="P141" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q141" s="2">
         <v>37.700000000000003</v>
@@ -10197,10 +10196,10 @@
         <v>0.2</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T141" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:20" x14ac:dyDescent="0.2">
@@ -10229,7 +10228,7 @@
         <v>23</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J142" s="5">
         <v>1.5127314814814816E-2</v>
@@ -10250,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P142" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q142" s="2">
         <v>29.95</v>
@@ -10259,10 +10258,10 @@
         <v>0.183</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T142" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143" spans="1:20" x14ac:dyDescent="0.2">
@@ -10300,7 +10299,7 @@
         <v>1.224537037037037E-2</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M143" s="1">
         <v>53047</v>
@@ -10312,7 +10311,7 @@
         <v>1</v>
       </c>
       <c r="P143" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q143" s="2">
         <v>15.167</v>
@@ -10321,10 +10320,10 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T143" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.2">
@@ -10374,7 +10373,7 @@
         <v>1</v>
       </c>
       <c r="P144" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q144" s="2">
         <v>25.95</v>
@@ -10383,10 +10382,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T144" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.2">
@@ -10436,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q145" s="2">
         <v>6.9669999999999996</v>
@@ -10445,10 +10444,10 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="S145" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T145" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.2">
@@ -10498,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="P146" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q146" s="2">
         <v>34.35</v>
@@ -10507,10 +10506,10 @@
         <v>5.7329999999999997</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T146" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.2">
@@ -10539,7 +10538,7 @@
         <v>24</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J147" s="5">
         <v>6.5416666666666665E-2</v>
@@ -10560,7 +10559,7 @@
         <v>1</v>
       </c>
       <c r="P147" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q147" s="2">
         <v>16.332999999999998</v>
@@ -10569,10 +10568,10 @@
         <v>8.7330000000000005</v>
       </c>
       <c r="S147" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T147" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.2">
@@ -10601,7 +10600,7 @@
         <v>75</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J148" s="5">
         <v>0.21687500000000001</v>
@@ -10610,7 +10609,7 @@
         <v>5.2106481481481483E-2</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M148" s="1">
         <v>123000</v>
@@ -10622,7 +10621,7 @@
         <v>1</v>
       </c>
       <c r="P148" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q148" s="2">
         <v>56.167000000000002</v>
@@ -10631,10 +10630,10 @@
         <v>10.867000000000001</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T148" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:20" x14ac:dyDescent="0.2">
@@ -10663,7 +10662,7 @@
         <v>25</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J149" s="5">
         <v>6.4282407407407413E-2</v>
@@ -10684,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q149" s="2">
         <v>28.35</v>
@@ -10693,10 +10692,10 @@
         <v>8.8170000000000002</v>
       </c>
       <c r="S149" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T149" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.2">
@@ -10725,7 +10724,7 @@
         <v>22</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J150" s="5">
         <v>4.4756944444444446E-2</v>
@@ -10734,7 +10733,7 @@
         <v>2.9224537037037038E-2</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M150" s="1">
         <v>122998</v>
@@ -10746,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="P150" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q150" s="2">
         <v>22.332999999999998</v>
@@ -10755,10 +10754,10 @@
         <v>4.367</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T150" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.2">
@@ -10808,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="P151" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q151" s="2">
         <v>55.767000000000003</v>
@@ -10817,10 +10816,10 @@
         <v>5.5830000000000002</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T151" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.2">
@@ -10849,7 +10848,7 @@
         <v>41</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J152" s="5">
         <v>0.20355324074074074</v>
@@ -10858,7 +10857,7 @@
         <v>5.4340277777777779E-2</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M152" s="1">
         <v>122995</v>
@@ -10870,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="P152" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q152" s="2">
         <v>22.582999999999998</v>
@@ -10879,10 +10878,10 @@
         <v>7.633</v>
       </c>
       <c r="S152" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T152" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.2">
@@ -10932,7 +10931,7 @@
         <v>1</v>
       </c>
       <c r="P153" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q153" s="2">
         <v>52.95</v>
@@ -10941,10 +10940,10 @@
         <v>5.1669999999999998</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T153" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.2">
@@ -10994,7 +10993,7 @@
         <v>1</v>
       </c>
       <c r="P154" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q154" s="2">
         <v>46.133000000000003</v>
@@ -11003,10 +11002,10 @@
         <v>13.45</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T154" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.2">
@@ -11035,7 +11034,7 @@
         <v>26</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J155" s="5">
         <v>0.21518518518518517</v>
@@ -11044,7 +11043,7 @@
         <v>5.3217592592592594E-2</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M155" s="1">
         <v>122993</v>
@@ -11056,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="P155" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q155" s="2">
         <v>55.866999999999997</v>
@@ -11065,10 +11064,10 @@
         <v>14</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T155" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.2">
@@ -11118,7 +11117,7 @@
         <v>1</v>
       </c>
       <c r="P156" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q156" s="2">
         <v>27.266999999999999</v>
@@ -11127,10 +11126,10 @@
         <v>10.967000000000001</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T156" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.2">
@@ -11159,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J157" s="5">
         <v>2.8298611111111111E-2</v>
@@ -11168,7 +11167,7 @@
         <v>1.7523148148148149E-2</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M157" s="1">
         <v>122991</v>
@@ -11180,7 +11179,7 @@
         <v>1</v>
       </c>
       <c r="P157" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q157" s="2">
         <v>10.266999999999999</v>
@@ -11189,10 +11188,10 @@
         <v>5.6</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T157" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.2">
@@ -11242,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="P158" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q158" s="2">
         <v>33.417000000000002</v>
@@ -11251,10 +11250,10 @@
         <v>7.3330000000000002</v>
       </c>
       <c r="S158" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T158" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="159" spans="1:20" x14ac:dyDescent="0.2">
@@ -11283,7 +11282,7 @@
         <v>26</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J159" s="5">
         <v>0.30413194444444441</v>
@@ -11292,7 +11291,7 @@
         <v>5.0243055555555555E-2</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M159" s="1">
         <v>122989</v>
@@ -11304,7 +11303,7 @@
         <v>1</v>
       </c>
       <c r="P159" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q159" s="2">
         <v>48.183</v>
@@ -11313,10 +11312,10 @@
         <v>11.433</v>
       </c>
       <c r="S159" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T159" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.2">
@@ -11345,7 +11344,7 @@
         <v>21</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J160" s="5">
         <v>0.29251157407407408</v>
@@ -11354,7 +11353,7 @@
         <v>3.7557870370370373E-2</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M160" s="1">
         <v>122988</v>
@@ -11366,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="P160" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q160" s="2">
         <v>26.167000000000002</v>
@@ -11375,10 +11374,10 @@
         <v>19.466999999999999</v>
       </c>
       <c r="S160" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T160" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="161" spans="1:20" x14ac:dyDescent="0.2">
@@ -11428,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q161" s="2">
         <v>26.4</v>
@@ -11437,10 +11436,10 @@
         <v>2.383</v>
       </c>
       <c r="S161" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T161" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="162" spans="1:20" x14ac:dyDescent="0.2">
@@ -11469,7 +11468,7 @@
         <v>29</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J162" s="5">
         <v>0.18995370370370371</v>
@@ -11478,7 +11477,7 @@
         <v>0.1037037037037037</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M162" s="1">
         <v>122986</v>
@@ -11499,10 +11498,10 @@
         <v>9.1170000000000009</v>
       </c>
       <c r="S162" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T162" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="163" spans="1:20" x14ac:dyDescent="0.2">
@@ -11531,7 +11530,7 @@
         <v>26</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J163" s="5">
         <v>0.2864814814814815</v>
@@ -11561,10 +11560,10 @@
         <v>61.017000000000003</v>
       </c>
       <c r="S163" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T163" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="164" spans="1:20" x14ac:dyDescent="0.2">
@@ -11623,10 +11622,10 @@
         <v>4.6829999999999998</v>
       </c>
       <c r="S164" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T164" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:20" x14ac:dyDescent="0.2">
@@ -11655,7 +11654,7 @@
         <v>43</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J165" s="5">
         <v>0.25890046296296293</v>
@@ -11664,7 +11663,7 @@
         <v>7.0567129629629632E-2</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M165" s="1">
         <v>122983</v>
@@ -11685,10 +11684,10 @@
         <v>16.332999999999998</v>
       </c>
       <c r="S165" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T165" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166" spans="1:20" x14ac:dyDescent="0.2">
@@ -11747,10 +11746,10 @@
         <v>0.2</v>
       </c>
       <c r="S166" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T166" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="167" spans="1:20" x14ac:dyDescent="0.2">
@@ -11779,7 +11778,7 @@
         <v>28</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J167" s="5">
         <v>0.21393518518518517</v>
@@ -11788,7 +11787,7 @@
         <v>5.3159722222222226E-2</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M167" s="1">
         <v>122981</v>
@@ -11809,10 +11808,10 @@
         <v>1.4330000000000001</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T167" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.2">
@@ -11841,7 +11840,7 @@
         <v>39</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J168" s="5">
         <v>0.1996064814814815</v>
@@ -11850,7 +11849,7 @@
         <v>3.9386574074074074E-2</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M168" s="1">
         <v>122980</v>
@@ -11871,10 +11870,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T168" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.2">
@@ -11912,7 +11911,7 @@
         <v>3.0601851851851852E-2</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M169" s="1">
         <v>53038</v>
@@ -11933,10 +11932,10 @@
         <v>3.7</v>
       </c>
       <c r="S169" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T169" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="1:20" x14ac:dyDescent="0.2">
@@ -11965,7 +11964,7 @@
         <v>28</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J170" s="5">
         <v>0.16083333333333333</v>
@@ -11974,7 +11973,7 @@
         <v>4.280092592592593E-2</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M170" s="1">
         <v>122979</v>
@@ -11995,10 +11994,10 @@
         <v>8.9</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T170" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="171" spans="1:20" x14ac:dyDescent="0.2">
@@ -12057,10 +12056,10 @@
         <v>13.25</v>
       </c>
       <c r="S171" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T171" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="172" spans="1:20" x14ac:dyDescent="0.2">
@@ -12086,10 +12085,10 @@
         <v>800000013</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J172" s="5">
         <v>0.14686342592592591</v>
@@ -12098,7 +12097,7 @@
         <v>4.9016203703703708E-2</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M172" s="1">
         <v>122977</v>
@@ -12110,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q172" s="2">
         <v>29.417000000000002</v>
@@ -12119,10 +12118,10 @@
         <v>40.133000000000003</v>
       </c>
       <c r="S172" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T172" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="173" spans="1:20" x14ac:dyDescent="0.2">
@@ -12181,10 +12180,10 @@
         <v>11.433</v>
       </c>
       <c r="S173" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T173" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="174" spans="1:20" x14ac:dyDescent="0.2">
@@ -12243,10 +12242,10 @@
         <v>2.617</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T174" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="175" spans="1:20" x14ac:dyDescent="0.2">
@@ -12296,7 +12295,7 @@
         <v>1</v>
       </c>
       <c r="P175" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q175" s="2">
         <v>24.8</v>
@@ -12305,10 +12304,10 @@
         <v>0.35</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T175" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="176" spans="1:20" x14ac:dyDescent="0.2">
@@ -12346,7 +12345,7 @@
         <v>1.1400462962962965E-2</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M176" s="1">
         <v>53034</v>
@@ -12358,7 +12357,7 @@
         <v>1</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q176" s="2">
         <v>12.117000000000001</v>
@@ -12367,10 +12366,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T176" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:20" x14ac:dyDescent="0.2">
@@ -12399,7 +12398,7 @@
         <v>29</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J177" s="5">
         <v>7.0324074074074081E-2</v>
@@ -12408,7 +12407,7 @@
         <v>0.10251157407407407</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M177" s="1">
         <v>122975</v>
@@ -12420,7 +12419,7 @@
         <v>1</v>
       </c>
       <c r="P177" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q177" s="2">
         <v>144.61699999999999</v>
@@ -12429,10 +12428,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T177" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="178" spans="1:20" x14ac:dyDescent="0.2">
@@ -12482,7 +12481,7 @@
         <v>1</v>
       </c>
       <c r="P178" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q178" s="2">
         <v>29.016999999999999</v>
@@ -12491,10 +12490,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T178" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="179" spans="1:20" x14ac:dyDescent="0.2">
@@ -12532,7 +12531,7 @@
         <v>6.9097222222222225E-3</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M179" s="1">
         <v>53032</v>
@@ -12544,7 +12543,7 @@
         <v>1</v>
       </c>
       <c r="P179" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q179" s="2">
         <v>1.7170000000000001</v>
@@ -12553,10 +12552,10 @@
         <v>0.15</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T179" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.2">
@@ -12606,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P180" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q180" s="2">
         <v>17.600000000000001</v>
@@ -12615,10 +12614,10 @@
         <v>15</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T180" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.2">
@@ -12647,7 +12646,7 @@
         <v>24</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J181" s="5">
         <v>1.2581018518518519E-2</v>
@@ -12656,7 +12655,7 @@
         <v>4.0555555555555553E-2</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M181" s="1">
         <v>122974</v>
@@ -12668,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q181" s="2">
         <v>43.267000000000003</v>
@@ -12677,10 +12676,10 @@
         <v>0.2</v>
       </c>
       <c r="S181" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T181" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="182" spans="1:20" x14ac:dyDescent="0.2">
@@ -12709,7 +12708,7 @@
         <v>22</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J182" s="5">
         <v>2.6504629629629628E-2</v>
@@ -12718,7 +12717,7 @@
         <v>4.08912037037037E-2</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M182" s="1">
         <v>122973</v>
@@ -12730,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="P182" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q182" s="2">
         <v>46.1</v>
@@ -12739,10 +12738,10 @@
         <v>0.183</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T182" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.2">
@@ -12780,7 +12779,7 @@
         <v>2.0254629629629629E-2</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M183" s="1">
         <v>53030</v>
@@ -12792,7 +12791,7 @@
         <v>1</v>
       </c>
       <c r="P183" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q183" s="2">
         <v>21.55</v>
@@ -12801,10 +12800,10 @@
         <v>0.217</v>
       </c>
       <c r="S183" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T183" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.2">
@@ -12833,7 +12832,7 @@
         <v>22</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J184" s="5">
         <v>3.3483796296296296E-2</v>
@@ -12854,7 +12853,7 @@
         <v>1</v>
       </c>
       <c r="P184" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q184" s="2">
         <v>31.567</v>
@@ -12863,10 +12862,10 @@
         <v>0.2</v>
       </c>
       <c r="S184" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T184" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="185" spans="1:20" x14ac:dyDescent="0.2">
@@ -12916,7 +12915,7 @@
         <v>1</v>
       </c>
       <c r="P185" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q185" s="2">
         <v>2.0830000000000002</v>
@@ -12925,10 +12924,10 @@
         <v>20.149999999999999</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T185" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="186" spans="1:20" x14ac:dyDescent="0.2">
@@ -12978,7 +12977,7 @@
         <v>1</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q186" s="2">
         <v>53.183</v>
@@ -12987,10 +12986,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T186" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="187" spans="1:20" x14ac:dyDescent="0.2">
@@ -13019,7 +13018,7 @@
         <v>24</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J187" s="5">
         <v>2.614583333333333E-2</v>
@@ -13028,7 +13027,7 @@
         <v>4.6689814814814816E-2</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M187" s="1">
         <v>122971</v>
@@ -13040,7 +13039,7 @@
         <v>1</v>
       </c>
       <c r="P187" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q187" s="2">
         <v>59.616999999999997</v>
@@ -13049,10 +13048,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S187" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T187" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.2">
@@ -13081,7 +13080,7 @@
         <v>31</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J188" s="5">
         <v>1.7199074074074071E-2</v>
@@ -13102,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="P188" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q188" s="2">
         <v>30.266999999999999</v>
@@ -13111,10 +13110,10 @@
         <v>0.15</v>
       </c>
       <c r="S188" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T188" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.2">
@@ -13152,7 +13151,7 @@
         <v>1.5185185185185185E-2</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M189" s="1">
         <v>53027</v>
@@ -13164,7 +13163,7 @@
         <v>1</v>
       </c>
       <c r="P189" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q189" s="2">
         <v>13.15</v>
@@ -13173,10 +13172,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S189" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T189" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.2">
@@ -13226,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="P190" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q190" s="2">
         <v>13.75</v>
@@ -13235,10 +13234,10 @@
         <v>7.45</v>
       </c>
       <c r="S190" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T190" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.2">
@@ -13288,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P191" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q191" s="2">
         <v>39.299999999999997</v>
@@ -13297,10 +13296,10 @@
         <v>6.0170000000000003</v>
       </c>
       <c r="S191" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T191" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="192" spans="1:20" x14ac:dyDescent="0.2">
@@ -13350,7 +13349,7 @@
         <v>1</v>
       </c>
       <c r="P192" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q192" s="2">
         <v>29.983000000000001</v>
@@ -13359,10 +13358,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S192" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T192" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="193" spans="1:20" x14ac:dyDescent="0.2">
@@ -13391,7 +13390,7 @@
         <v>22</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J193" s="5">
         <v>1.1574074074074075E-2</v>
@@ -13400,7 +13399,7 @@
         <v>1.9409722222222221E-2</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M193" s="1">
         <v>122967</v>
@@ -13412,7 +13411,7 @@
         <v>1</v>
       </c>
       <c r="P193" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q193" s="2">
         <v>16.266999999999999</v>
@@ -13421,10 +13420,10 @@
         <v>7.367</v>
       </c>
       <c r="S193" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T193" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="194" spans="1:20" x14ac:dyDescent="0.2">
@@ -13474,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="P194" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q194" s="2">
         <v>15.683</v>
@@ -13483,10 +13482,10 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T194" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="195" spans="1:20" x14ac:dyDescent="0.2">
@@ -13515,7 +13514,7 @@
         <v>75</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J195" s="5">
         <v>4.5324074074074072E-2</v>
@@ -13524,7 +13523,7 @@
         <v>4.670138888888889E-2</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M195" s="1">
         <v>122965</v>
@@ -13536,7 +13535,7 @@
         <v>1</v>
       </c>
       <c r="P195" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q195" s="2">
         <v>45.982999999999997</v>
@@ -13545,10 +13544,10 @@
         <v>16.05</v>
       </c>
       <c r="S195" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T195" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="196" spans="1:20" x14ac:dyDescent="0.2">
@@ -13577,7 +13576,7 @@
         <v>24</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J196" s="5">
         <v>2.5949074074074072E-2</v>
@@ -13586,7 +13585,7 @@
         <v>3.5694444444444445E-2</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M196" s="1">
         <v>122964</v>
@@ -13598,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="P196" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q196" s="2">
         <v>46.582999999999998</v>
@@ -13607,10 +13606,10 @@
         <v>1.9</v>
       </c>
       <c r="S196" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T196" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.2">
@@ -13660,7 +13659,7 @@
         <v>1</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q197" s="2">
         <v>150.417</v>
@@ -13669,10 +13668,10 @@
         <v>11.233000000000001</v>
       </c>
       <c r="S197" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T197" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.2">
@@ -13701,7 +13700,7 @@
         <v>22</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J198" s="5">
         <v>2.8518518518518523E-2</v>
@@ -13710,7 +13709,7 @@
         <v>4.5254629629629624E-2</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M198" s="1">
         <v>122962</v>
@@ -13722,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q198" s="2">
         <v>55.232999999999997</v>
@@ -13731,10 +13730,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="S198" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T198" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.2">
@@ -13784,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="P199" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q199" s="2">
         <v>60.216999999999999</v>
@@ -13793,10 +13792,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S199" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T199" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="200" spans="1:20" x14ac:dyDescent="0.2">
@@ -13825,7 +13824,7 @@
         <v>29</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J200" s="5">
         <v>2.3136574074074077E-2</v>
@@ -13834,7 +13833,7 @@
         <v>7.2824074074074083E-2</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M200" s="1">
         <v>122960</v>
@@ -13846,7 +13845,7 @@
         <v>1</v>
       </c>
       <c r="P200" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q200" s="2">
         <v>36.832999999999998</v>
@@ -13855,10 +13854,10 @@
         <v>58.616999999999997</v>
       </c>
       <c r="S200" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T200" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="201" spans="1:20" x14ac:dyDescent="0.2">
@@ -13908,7 +13907,7 @@
         <v>1</v>
       </c>
       <c r="P201" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q201" s="2">
         <v>22.567</v>
@@ -13917,10 +13916,10 @@
         <v>18.649999999999999</v>
       </c>
       <c r="S201" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T201" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="202" spans="1:20" x14ac:dyDescent="0.2">
@@ -13949,7 +13948,7 @@
         <v>29</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J202" s="5">
         <v>1.7997685185185186E-2</v>
@@ -13958,7 +13957,7 @@
         <v>3.2442129629629633E-2</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M202" s="1">
         <v>122958</v>
@@ -13979,10 +13978,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S202" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T202" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="203" spans="1:20" x14ac:dyDescent="0.2">
@@ -14041,10 +14040,10 @@
         <v>12.882999999999999</v>
       </c>
       <c r="S203" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T203" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="204" spans="1:20" x14ac:dyDescent="0.2">
@@ -14073,7 +14072,7 @@
         <v>25</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J204" s="5">
         <v>5.917824074074074E-2</v>
@@ -14103,10 +14102,10 @@
         <v>9.0670000000000002</v>
       </c>
       <c r="S204" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T204" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="205" spans="1:20" x14ac:dyDescent="0.2">
@@ -14135,7 +14134,7 @@
         <v>27</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J205" s="5">
         <v>2.9571759259259259E-2</v>
@@ -14165,10 +14164,10 @@
         <v>11.217000000000001</v>
       </c>
       <c r="S205" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T205" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.2">
@@ -14206,7 +14205,7 @@
         <v>9.5358796296296289E-2</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M206" s="1">
         <v>122954</v>
@@ -14227,10 +14226,10 @@
         <v>14.05</v>
       </c>
       <c r="S206" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T206" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.2">
@@ -14256,10 +14255,10 @@
         <v>800000013</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J207" s="5">
         <v>1.8715277777777779E-2</v>
@@ -14268,7 +14267,7 @@
         <v>3.0532407407407411E-2</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M207" s="1">
         <v>122952</v>
@@ -14289,10 +14288,10 @@
         <v>8.0169999999999995</v>
       </c>
       <c r="S207" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T207" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208" spans="1:20" x14ac:dyDescent="0.2">
@@ -14321,7 +14320,7 @@
         <v>43</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J208" s="5">
         <v>6.1018518518518521E-2</v>
@@ -14330,7 +14329,7 @@
         <v>2.6956018518518522E-2</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M208" s="1">
         <v>122950</v>
@@ -14342,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="P208" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q208" s="2">
         <v>36.35</v>
@@ -14351,10 +14350,10 @@
         <v>0.61699999999999999</v>
       </c>
       <c r="S208" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T208" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="209" spans="1:20" x14ac:dyDescent="0.2">
@@ -14404,7 +14403,7 @@
         <v>1</v>
       </c>
       <c r="P209" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q209" s="2">
         <v>22.4</v>
@@ -14413,10 +14412,10 @@
         <v>0.1</v>
       </c>
       <c r="S209" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T209" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="210" spans="1:20" x14ac:dyDescent="0.2">
@@ -14454,7 +14453,7 @@
         <v>2.449074074074074E-2</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M210" s="1">
         <v>53022</v>
@@ -14466,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q210" s="2">
         <v>4.2169999999999996</v>
@@ -14475,10 +14474,10 @@
         <v>22.6</v>
       </c>
       <c r="S210" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T210" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="211" spans="1:20" x14ac:dyDescent="0.2">
@@ -14507,7 +14506,7 @@
         <v>21</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J211" s="5">
         <v>4.5555555555555551E-2</v>
@@ -14516,7 +14515,7 @@
         <v>0.1464351851851852</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M211" s="1">
         <v>122948</v>
@@ -14528,7 +14527,7 @@
         <v>1</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q211" s="2">
         <v>187.6</v>
@@ -14537,10 +14536,10 @@
         <v>0.15</v>
       </c>
       <c r="S211" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T211" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="212" spans="1:20" x14ac:dyDescent="0.2">
@@ -14590,7 +14589,7 @@
         <v>1</v>
       </c>
       <c r="P212" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q212" s="2">
         <v>23.5</v>
@@ -14599,10 +14598,10 @@
         <v>0.2</v>
       </c>
       <c r="S212" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T212" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="213" spans="1:20" x14ac:dyDescent="0.2">
@@ -14652,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="P213" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q213" s="2">
         <v>52.082999999999998</v>
@@ -14661,10 +14660,10 @@
         <v>6.867</v>
       </c>
       <c r="S213" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T213" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="214" spans="1:20" x14ac:dyDescent="0.2">
@@ -14702,7 +14701,7 @@
         <v>7.452546296296296E-2</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M214" s="1">
         <v>53019</v>
@@ -14714,7 +14713,7 @@
         <v>1</v>
       </c>
       <c r="P214" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q214" s="2">
         <v>8.3000000000000004E-2</v>
@@ -14723,10 +14722,10 @@
         <v>49.533000000000001</v>
       </c>
       <c r="S214" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T214" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="215" spans="1:20" x14ac:dyDescent="0.2">
@@ -14776,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q215" s="2">
         <v>5.5</v>
@@ -14785,10 +14784,10 @@
         <v>8.8330000000000002</v>
       </c>
       <c r="S215" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T215" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="216" spans="1:20" x14ac:dyDescent="0.2">
@@ -14817,7 +14816,7 @@
         <v>22</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J216" s="5">
         <v>1.4155092592592592E-2</v>
@@ -14826,7 +14825,7 @@
         <v>3.5636574074074077E-2</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M216" s="1">
         <v>122945</v>
@@ -14838,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P216" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q216" s="2">
         <v>39.366999999999997</v>
@@ -14847,10 +14846,10 @@
         <v>0.45</v>
       </c>
       <c r="S216" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T216" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="1:20" x14ac:dyDescent="0.2">
@@ -14900,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P217" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q217" s="2">
         <v>19.25</v>
@@ -14909,10 +14908,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S217" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T217" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="218" spans="1:20" x14ac:dyDescent="0.2">
@@ -14941,7 +14940,7 @@
         <v>22</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J218" s="5">
         <v>3.888888888888889E-2</v>
@@ -14962,7 +14961,7 @@
         <v>1</v>
       </c>
       <c r="P218" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q218" s="2">
         <v>107.56699999999999</v>
@@ -14971,10 +14970,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S218" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T218" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="219" spans="1:20" x14ac:dyDescent="0.2">
@@ -15024,7 +15023,7 @@
         <v>1</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q219" s="2">
         <v>17.766999999999999</v>
@@ -15033,10 +15032,10 @@
         <v>0.73299999999999998</v>
       </c>
       <c r="S219" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T219" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="220" spans="1:20" x14ac:dyDescent="0.2">
@@ -15074,7 +15073,7 @@
         <v>1.5046296296296295E-2</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M220" s="1">
         <v>53014</v>
@@ -15086,7 +15085,7 @@
         <v>1</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q220" s="2">
         <v>16.067</v>
@@ -15095,10 +15094,10 @@
         <v>0.15</v>
       </c>
       <c r="S220" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T220" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="221" spans="1:20" x14ac:dyDescent="0.2">
@@ -15127,7 +15126,7 @@
         <v>23</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J221" s="5">
         <v>4.3379629629629629E-2</v>
@@ -15148,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="P221" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q221" s="2">
         <v>39.167000000000002</v>
@@ -15157,10 +15156,10 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="S221" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T221" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="222" spans="1:20" x14ac:dyDescent="0.2">
@@ -15189,7 +15188,7 @@
         <v>31</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J222" s="5">
         <v>3.2256944444444442E-2</v>
@@ -15198,7 +15197,7 @@
         <v>4.7905092592592589E-2</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M222" s="1">
         <v>122941</v>
@@ -15210,7 +15209,7 @@
         <v>1</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q222" s="2">
         <v>62.7</v>
@@ -15219,10 +15218,10 @@
         <v>0.15</v>
       </c>
       <c r="S222" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T222" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="223" spans="1:20" x14ac:dyDescent="0.2">
@@ -15251,7 +15250,7 @@
         <v>24</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J223" s="5">
         <v>3.349537037037037E-2</v>
@@ -15260,7 +15259,7 @@
         <v>4.4814814814814814E-2</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M223" s="1">
         <v>122940</v>
@@ -15272,7 +15271,7 @@
         <v>1</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q223" s="2">
         <v>51.9</v>
@@ -15281,10 +15280,10 @@
         <v>5.25</v>
       </c>
       <c r="S223" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T223" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="224" spans="1:20" x14ac:dyDescent="0.2">
@@ -15334,7 +15333,7 @@
         <v>1</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q224" s="2">
         <v>11.5</v>
@@ -15343,10 +15342,10 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="S224" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T224" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="225" spans="1:20" x14ac:dyDescent="0.2">
@@ -15396,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="P225" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q225" s="2">
         <v>14.667</v>
@@ -15405,10 +15404,10 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="S225" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T225" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="226" spans="1:20" x14ac:dyDescent="0.2">
@@ -15446,7 +15445,7 @@
         <v>1.6087962962962964E-2</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M226" s="1">
         <v>53011</v>
@@ -15458,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q226" s="2">
         <v>16.533000000000001</v>
@@ -15467,10 +15466,10 @@
         <v>0.15</v>
       </c>
       <c r="S226" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T226" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="227" spans="1:20" x14ac:dyDescent="0.2">
@@ -15520,7 +15519,7 @@
         <v>1</v>
       </c>
       <c r="P227" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q227" s="2">
         <v>39.716999999999999</v>
@@ -15529,10 +15528,10 @@
         <v>5.9329999999999998</v>
       </c>
       <c r="S227" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T227" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="228" spans="1:20" x14ac:dyDescent="0.2">
@@ -15561,7 +15560,7 @@
         <v>23</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J228" s="5">
         <v>2.1296296296296299E-2</v>
@@ -15570,7 +15569,7 @@
         <v>1.6018518518518519E-2</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M228" s="1">
         <v>122938</v>
@@ -15582,7 +15581,7 @@
         <v>1</v>
       </c>
       <c r="P228" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q228" s="2">
         <v>8.75</v>
@@ -15591,10 +15590,10 @@
         <v>11.382999999999999</v>
       </c>
       <c r="S228" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T228" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="229" spans="1:20" x14ac:dyDescent="0.2">
@@ -15623,7 +15622,7 @@
         <v>25</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J229" s="5">
         <v>1.238425925925926E-2</v>
@@ -15632,7 +15631,7 @@
         <v>7.149305555555556E-2</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M229" s="1">
         <v>122937</v>
@@ -15644,7 +15643,7 @@
         <v>1</v>
       </c>
       <c r="P229" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q229" s="2">
         <v>66.8</v>
@@ -15653,10 +15652,10 @@
         <v>28.167000000000002</v>
       </c>
       <c r="S229" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T229" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="230" spans="1:20" x14ac:dyDescent="0.2">
@@ -15685,7 +15684,7 @@
         <v>23</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J230" s="5">
         <v>1.4259259259259261E-2</v>
@@ -15694,7 +15693,7 @@
         <v>1.6550925925925924E-2</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M230" s="1">
         <v>122936</v>
@@ -15706,7 +15705,7 @@
         <v>1</v>
       </c>
       <c r="P230" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q230" s="2">
         <v>12.9</v>
@@ -15715,10 +15714,10 @@
         <v>6.3170000000000002</v>
       </c>
       <c r="S230" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T230" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="1:20" x14ac:dyDescent="0.2">
@@ -15768,7 +15767,7 @@
         <v>1</v>
       </c>
       <c r="P231" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q231" s="2">
         <v>34.332999999999998</v>
@@ -15777,10 +15776,10 @@
         <v>9.35</v>
       </c>
       <c r="S231" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T231" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CB6197-A029-2948-88C5-EE76E3102154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4BBD9D-8558-8347-9835-F59FD6AB24DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="32860" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semana 10" sheetId="1" r:id="rId1"/>
+    <sheet name="Semana 11" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EC71C1-46DD-7443-96B9-D5D39E0FACBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CFFBC0-0BE9-A143-8B3E-B0F7EDB2D530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semana 20" sheetId="1" r:id="rId1"/>
+    <sheet name="Semana 21" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AEFEDE-4478-374A-80B2-8A9196D50B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7D8078-F36E-9D4C-83D5-30F4DC5FBCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semana 21" sheetId="1" r:id="rId1"/>
+    <sheet name="Semana 22" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Trazabilidad Logistica.xlsx
+++ b/Trazabilidad Logistica.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvarez/Desktop/IT Solutions/2024/ECSA/Reporte/Plano Trazab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCC4459-DFE3-6047-9F44-51ED658ADC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5243A86-44AE-9D45-BA2B-35D8677D850F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18360" xr2:uid="{BE95434F-D71E-444E-AFE1-9260706183DC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semana 29" sheetId="1" r:id="rId1"/>
+    <sheet name="Semana 30" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
